--- a/data/trans_camb/IP21-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,08</t>
+          <t>-2,63; 4,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,53</t>
+          <t>-2,22; 6,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,65</t>
+          <t>-5,31; -0,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,48</t>
+          <t>-4,84; 4,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 2,44</t>
+          <t>-7,64; 1,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 7,64</t>
+          <t>-5,24; 7,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,18</t>
+          <t>-2,74; 2,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,58</t>
+          <t>-3,56; 2,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,89</t>
+          <t>-3,8; 3,57</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 380,96</t>
+          <t>-80,41; 354,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 233,26</t>
+          <t>-68,19; 179,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 317,68</t>
+          <t>-85,8; 175,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 259,68</t>
+          <t>-100,0; 371,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,1</t>
+          <t>-1,14; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,27</t>
+          <t>-3,41; 0,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -1,28</t>
+          <t>-4,76; -1,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,62</t>
+          <t>-2,97; 1,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,14</t>
+          <t>-4,2; 0,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; -1,91</t>
+          <t>-5,7; -1,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,71</t>
+          <t>-1,55; 1,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,54</t>
+          <t>-3,25; -0,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; -2,2</t>
+          <t>-4,68; -2,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 108,14</t>
+          <t>-23,06; 116,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 10,83</t>
+          <t>-66,05; 13,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,56; -34,38</t>
+          <t>-86,89; -38,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 42,8</t>
+          <t>-47,0; 41,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,75; 0,02</t>
+          <t>-65,79; 5,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,64; -42,94</t>
+          <t>-86,63; -41,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 42,79</t>
+          <t>-28,88; 42,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -13,54</t>
+          <t>-60,67; -12,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,8; -52,19</t>
+          <t>-82,56; -50,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 2,04</t>
+          <t>-4,3; 1,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,95</t>
+          <t>-2,94; 3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,9</t>
+          <t>-4,56; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,11</t>
+          <t>-2,0; 4,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,43</t>
+          <t>-3,89; 2,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,43</t>
+          <t>-5,09; 0,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,31</t>
+          <t>-2,38; 2,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,91</t>
+          <t>-2,4; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,37</t>
+          <t>-3,81; 0,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 112,18</t>
+          <t>-80,23; 89,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 194,67</t>
+          <t>-57,94; 186,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,89; 117,86</t>
+          <t>-82,12; 111,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 294,35</t>
+          <t>-48,16; 277,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 167,36</t>
+          <t>-71,2; 138,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 82,65</t>
+          <t>-93,64; 51,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 93,91</t>
+          <t>-50,09; 97,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 71,4</t>
+          <t>-50,85; 84,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 18,3</t>
+          <t>-76,6; 15,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,96</t>
+          <t>-1,25; 1,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,88</t>
+          <t>-2,23; 0,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,99</t>
+          <t>-3,67; -1,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,75</t>
+          <t>-2,01; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,15</t>
+          <t>-3,43; -0,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -1,43</t>
+          <t>-4,54; -1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,23</t>
+          <t>-1,21; 1,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,16</t>
+          <t>-2,37; -0,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -1,66</t>
+          <t>-3,78; -1,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 65,78</t>
+          <t>-28,2; 61,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 30,64</t>
+          <t>-49,63; 29,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,01; -27,71</t>
+          <t>-81,22; -32,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 46,93</t>
+          <t>-36,13; 40,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,63; -3,12</t>
+          <t>-62,29; -3,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,83; -36,64</t>
+          <t>-80,51; -39,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 33,77</t>
+          <t>-25,08; 35,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,78; -4,12</t>
+          <t>-48,47; -4,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,14; -44,23</t>
+          <t>-76,71; -42,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,07</t>
+          <t>-2,65; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,42</t>
+          <t>-2,47; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -0,64</t>
+          <t>-5,96; -0,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,3</t>
+          <t>-4,74; 4,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 1,31</t>
+          <t>-6,98; 1,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,38</t>
+          <t>-5,02; 9,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,78</t>
+          <t>-2,76; 2,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,46</t>
+          <t>-3,35; 2,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,57</t>
+          <t>-3,79; 3,71</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 354,53</t>
+          <t>-80,99; 273,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 179,39</t>
+          <t>-66,73; 188,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,8; 175,42</t>
+          <t>-84,92; 215,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 371,77</t>
+          <t>-100,0; 315,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,13</t>
+          <t>-1,44; 3,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,31</t>
+          <t>-3,41; 0,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -1,37</t>
+          <t>-4,62; -1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,57</t>
+          <t>-3,01; 1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,12</t>
+          <t>-4,1; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; -1,86</t>
+          <t>-5,55; -2,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,65</t>
+          <t>-1,55; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,47</t>
+          <t>-3,17; -0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -2,07</t>
+          <t>-4,62; -2,09</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 116,85</t>
+          <t>-27,86; 102,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,05; 13,62</t>
+          <t>-65,24; 17,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,89; -38,68</t>
+          <t>-87,71; -33,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 41,29</t>
+          <t>-46,14; 42,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 5,75</t>
+          <t>-66,09; 7,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,63; -41,76</t>
+          <t>-85,29; -47,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 42,74</t>
+          <t>-28,51; 46,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -12,92</t>
+          <t>-59,41; -9,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,56; -50,3</t>
+          <t>-83,57; -53,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,7</t>
+          <t>-4,52; 1,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,78</t>
+          <t>-2,68; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,91</t>
+          <t>-4,34; 1,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,71</t>
+          <t>-2,03; 5,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,13</t>
+          <t>-3,86; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,46</t>
+          <t>-4,68; 0,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,49</t>
+          <t>-2,33; 2,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,06</t>
+          <t>-2,36; 2,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,2</t>
+          <t>-3,66; 0,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 89,41</t>
+          <t>-78,33; 98,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 186,68</t>
+          <t>-53,29; 188,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 111,28</t>
+          <t>-82,03; 102,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 277,13</t>
+          <t>-43,91; 344,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 138,97</t>
+          <t>-74,01; 124,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-93,64; 51,0</t>
+          <t>-90,49; 113,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 97,9</t>
+          <t>-46,6; 106,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 84,18</t>
+          <t>-50,64; 79,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,6; 15,72</t>
+          <t>-78,47; 17,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,83</t>
+          <t>-1,43; 1,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,84</t>
+          <t>-2,18; 0,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -1,03</t>
+          <t>-3,76; -1,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,51</t>
+          <t>-2,08; 1,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,19</t>
+          <t>-3,39; -0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -1,69</t>
+          <t>-4,36; -1,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,24</t>
+          <t>-1,11; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; -0,17</t>
+          <t>-2,4; -0,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -1,65</t>
+          <t>-3,65; -1,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 61,66</t>
+          <t>-30,8; 66,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 29,61</t>
+          <t>-49,13; 25,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,22; -32,97</t>
+          <t>-79,83; -31,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 40,76</t>
+          <t>-37,16; 42,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,29; -3,42</t>
+          <t>-62,05; -2,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,51; -39,39</t>
+          <t>-79,44; -35,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 35,08</t>
+          <t>-23,45; 36,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,47; -4,03</t>
+          <t>-49,89; -4,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,71; -42,74</t>
+          <t>-75,11; -44,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-2,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,56</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,92</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,4</t>
+          <t>-4,74; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,41</t>
+          <t>-6,86; 2,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -0,65</t>
+          <t>-4,93; 8,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,28</t>
+          <t>-2,62; 4,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,41</t>
+          <t>-1,98; 6,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 9,08</t>
+          <t>-5,38; -0,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,95</t>
+          <t>-2,66; 3,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,51</t>
+          <t>-3,18; 2,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,71</t>
+          <t>-3,63; 4,98</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-4,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-66,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-5,99%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>59,71%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-66,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-11,7%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-37,74%</t>
+          <t>-31,62%</t>
         </is>
       </c>
     </row>
@@ -783,24 +783,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-82,08; 380,96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-80,99; 273,18</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,73; 188,69</t>
+          <t>-64,44; 233,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,92; 215,73</t>
+          <t>-80,82; 317,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 315,47</t>
+          <t>-100,0; 341,27</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,67</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,5</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,14</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-3,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,01</t>
+          <t>-2,99; 1,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,37</t>
+          <t>-4,48; -0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,24</t>
+          <t>-5,82; -1,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,68</t>
+          <t>-1,24; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,09</t>
+          <t>-3,55; 0,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -2,1</t>
+          <t>-4,59; -1,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,75</t>
+          <t>-1,6; 1,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; -0,42</t>
+          <t>-3,27; -0,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -2,09</t>
+          <t>-4,72; -2,19</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-12,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-41,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-71,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>20,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-36,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-70,85%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-12,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-41,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-70,77%</t>
+          <t>-70,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-70,84%</t>
+          <t>-71,15%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 102,04</t>
+          <t>-46,93; 42,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 17,6</t>
+          <t>-66,75; 0,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,71; -33,58</t>
+          <t>-86,83; -43,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 42,16</t>
+          <t>-26,39; 108,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 7,28</t>
+          <t>-66,59; 10,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,29; -47,12</t>
+          <t>-87,98; -29,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 46,95</t>
+          <t>-28,68; 42,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,41; -9,84</t>
+          <t>-60,51; -13,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,57; -53,94</t>
+          <t>-82,98; -51,97</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,61</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,99</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,61</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,84</t>
+          <t>-2,19; 5,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,73</t>
+          <t>-3,5; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,85</t>
+          <t>-5,0; 0,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,22</t>
+          <t>-4,22; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,11</t>
+          <t>-2,71; 3,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,87</t>
+          <t>-4,59; 1,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,53</t>
+          <t>-2,31; 2,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,07</t>
+          <t>-2,4; 1,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,29</t>
+          <t>-3,75; 0,24</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39,35%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-18,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-59,38%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-30,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-34,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-18,18%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-57,84%</t>
+          <t>-35,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-46,88%</t>
+          <t>-47,9%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,33; 98,87</t>
+          <t>-48,69; 294,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 188,67</t>
+          <t>-70,43; 167,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 102,89</t>
+          <t>-92,03; 70,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 344,4</t>
+          <t>-78,96; 112,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 124,07</t>
+          <t>-50,7; 194,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,49; 113,74</t>
+          <t>-83,61; 109,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 106,48</t>
+          <t>-50,08; 93,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 79,99</t>
+          <t>-50,75; 71,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,47; 17,7</t>
+          <t>-79,3; 17,13</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,98</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,95</t>
+          <t>-1,75; 1,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,8</t>
+          <t>-3,46; -0,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -1,08</t>
+          <t>-4,34; -1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,59</t>
+          <t>-1,41; 1,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; -0,22</t>
+          <t>-2,23; 0,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,4</t>
+          <t>-3,68; -0,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,26</t>
+          <t>-1,14; 1,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,18</t>
+          <t>-2,4; -0,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -1,71</t>
+          <t>-3,65; -1,64</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-3,45%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-39,49%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-64,81%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-19,09%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-62,78%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-3,45%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-39,49%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-64,39%</t>
+          <t>-62,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-63,57%</t>
+          <t>-63,66%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 66,89</t>
+          <t>-32,68; 46,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 25,8</t>
+          <t>-61,63; -3,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,83; -31,77</t>
+          <t>-80,88; -35,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 42,27</t>
+          <t>-31,31; 65,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,05; -2,79</t>
+          <t>-48,44; 30,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,44; -35,67</t>
+          <t>-79,93; -27,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 36,71</t>
+          <t>-24,21; 33,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,89; -4,25</t>
+          <t>-49,78; -4,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,11; -44,52</t>
+          <t>-76,22; -44,59</t>
         </is>
       </c>
     </row>
